--- a/FORMULARIO/CRONO.xlsx
+++ b/FORMULARIO/CRONO.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
   <si>
     <t xml:space="preserve">N</t>
   </si>
@@ -515,6 +515,12 @@
       </rPr>
       <t xml:space="preserve">(ASPLENIACEAE) DE LAS YUNGAS ARGENTINAS, MEDIANTE LA APLICACION DE TECNICAS DE LABORATORIO CONVENCIONALES.</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTUDIO DE PARÁMETROS REPRODUCTIVOS EN OVINOS CON VISTAS AL MEJORAMIENTO GENÉTICO EN LA ECOREGIÓN PUNA. PROVINCIA DE JUJUY </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPA DE FERTILIDAD CON USO DE VARIABLES FÍSICAS-QUÍMICAS DEL SUELO DEL CAMPO EXPERIMENTAL DR. EMILIO NAVEA, FCA-UNJu </t>
   </si>
 </sst>
 </file>
@@ -524,7 +530,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -561,6 +567,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri-BoldItalic"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -622,7 +636,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -634,8 +648,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -647,31 +661,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF6D"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -915,13 +904,13 @@
   <dimension ref="A1:C1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="91.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="91.98"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1158,7 +1147,7 @@
       <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1169,7 +1158,7 @@
       <c r="B23" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1180,7 +1169,7 @@
       <c r="B24" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1191,7 +1180,7 @@
       <c r="B25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1202,7 +1191,7 @@
       <c r="B26" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1213,7 +1202,7 @@
       <c r="B27" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="3" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1224,7 +1213,7 @@
       <c r="B28" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1235,7 +1224,7 @@
       <c r="B29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1246,7 +1235,7 @@
       <c r="B30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1257,8 +1246,30 @@
       <c r="B31" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="3" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/FORMULARIO/CRONO.xlsx
+++ b/FORMULARIO/CRONO.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
   <si>
     <t xml:space="preserve">N</t>
   </si>
@@ -521,6 +521,9 @@
   </si>
   <si>
     <t xml:space="preserve">MAPA DE FERTILIDAD CON USO DE VARIABLES FÍSICAS-QUÍMICAS DEL SUELO DEL CAMPO EXPERIMENTAL DR. EMILIO NAVEA, FCA-UNJu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROL DE CALIDAD FÍSICO-QUÍMICA EN VINOS ELABORADOS EN UNA BODEGA BOUTIQUE DE LA PROVINCIA DE JUJUY</t>
   </si>
 </sst>
 </file>
@@ -648,7 +651,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1272,6 +1275,17 @@
         <v>38</v>
       </c>
     </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/FORMULARIO/CRONO.xlsx
+++ b/FORMULARIO/CRONO.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Documents\JUAN\BYDE\2025\COMISIÓN JORNADAS INTEGRADAS 2025\POSTERS_JIA_FCAUNJU_2025\FORMULARIO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1094E19-7076-4932-B9E0-71D98DFFF504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,84 +25,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="40">
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Día</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trabajo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martes 16 de Septiembre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USO DE ASERRÍN Y COMPOST COMO SUSTRATOS ALTERNATIVOS EN LA PRODUCCIÓN DE PLANTINES DE ENTEROLOBIUM CONTORTISILIQUUM “PACARA” EN LA PROVINCIA DE JUJUY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERFIL PALINOLÓGICO Y NUTRICIONAL DEL POLEN APÍCOLA COSECHADO DURANTE LA CAMPAÑA 2024 -2025 EN SAN PEDRO JUJUY (ARGENTINA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVALUACIÓN MICROBIOLÓGICA DE LECHUGA (Lactuca sativa L.) PRODUCIDA EN HUERTAS ESCOLARES DEL DPTO. DR. MANUEL BELGRANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MODELADO DE PRECIOS MINORISTAS DE HORTALIZAS EN JUJUY: UN ENFOQUE BASADO EN MECANISMOS DE TRANSMISIÓN DE PRECIOS CON VECM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROMOCIÓN DE PRÁCTICAS SUSTENTABLES EN SISTEMAS HORTÍCOLAS: EXTRACTOS VEGETALES CON CAPACIDAD BIOENRAIZANTE, BIOFERTILIZANTE Y BIOPROTECTORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUERTA AGROECOLOGICA ESCOLAR: EL HUERTO DE COLORES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDUCACIÓN ALIMENTARIA EN LA FORMACIÓN DEL LICENCIADO EN BROMATOLOGÍA: EXPERIENCIAS DE CAPACITACIÓN EN CONTEXTOS REALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miércoles 17 de Septiembre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTUDIOS PRELIMINARES SOBRE LA PRESENCIA DE BACTERIAS DEL GÉNERO Pseudomonas spp. EN RÍOS DE LA QUEBRADA DE HUMAHUACA, DURANTE ÉPOCA LLUVIOSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DINÁMICA DE LA RESTAURACIÓN PASIVA, A PARTIR DE LA REGENERACIÓN, EN UN BOSQUE DISTURBADO DE LA SELVA PEDEMONTANA DE YUNGAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL PODCAST Y LA RADIO EN VIVO COMO HERRAMIENTAS PEDAGÓGICAS PARA GESTIÓN AMBIENTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTIMACIÓN DE ÍNDICES DE PRECIOS MAYORISTAS DE LAS PRINCIPALES FRUTAS Y HORTALIZAS RELEVADAS EN EL MERCADO FORMADOR DE PRECIOS DE LA REGIÓN DEL NOA ARGENTINO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TENDIENDO PUENTES ENTRE UNIVERSIDAD Y COMUNIDAD - PROYECTO “CRECE JUNTO A TU ÁRBOL”, VOLUNTARIADO UNIVERSITARIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANITAS LIMPIAS SALVAN VIDAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FACTORES QUE INFLUYEN EN LAS DIFICULTADES DE APRENDIZAJE EN QUÍMICA GENERAL: PERCEPCIONES DE ESTUDIANTES DE BROMATOLOGÍA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jueves 18 de Septiembre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMPLEMENTACIÓN DEL APRENDIZAJE BASADO EN PROYECTOS EN LAS ASIGNATURAS BIOESTADÍSTICA (LICENCIATURA EN CIENCIAS BIOLÓGICAS) Y ESTADÍSTICA (LICENCIATURA EN DESARROLLO RURAL) DE LA UNJU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPOSICIÓN QUÍMICA DE ACEITES ESENCIALES DE ROMERO (Rosmarinus officinalis) Y TOMILLO (Thymus vulgaris). ESTUDIO DE SUS PROPIEDADES ANTIMICROBIANAS FRENTE A BACTERIAS GRAM NEGATIVAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARACTERIZACIÓN FISICOQUÍMICA DE PELÍCULAS COMESTIBLES A BASE DE ALMIDÓN DE PAPA Y ÁCIDO CÍTRICO COMO ADITIVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVALUACIÓN DE PRÁCTICAS DEL USO DE SAL Y CONOCIMIENTOS EN PANADERÍAS DE LA PROVINCIA DE JUJUY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROL DE CALIDAD EN FRUTOS DE POMELO (Citrus paradisi): EVALUACIÓN DE LA CAPACIDAD DEL PROCESO EN PRECOSECHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVALUACIÓN IN VIVO DE EXTRACTOS DE PROPÓLEOS FRENTE A NOSEMA SP. EN APIS MELLIFERA DE LA PROVINCIA DE JUJUY</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="41">
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Día</t>
+  </si>
+  <si>
+    <t>Trabajo</t>
+  </si>
+  <si>
+    <t>Martes 16 de Septiembre</t>
+  </si>
+  <si>
+    <t>USO DE ASERRÍN Y COMPOST COMO SUSTRATOS ALTERNATIVOS EN LA PRODUCCIÓN DE PLANTINES DE ENTEROLOBIUM CONTORTISILIQUUM “PACARA” EN LA PROVINCIA DE JUJUY</t>
+  </si>
+  <si>
+    <t>PERFIL PALINOLÓGICO Y NUTRICIONAL DEL POLEN APÍCOLA COSECHADO DURANTE LA CAMPAÑA 2024 -2025 EN SAN PEDRO JUJUY (ARGENTINA)</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN MICROBIOLÓGICA DE LECHUGA (Lactuca sativa L.) PRODUCIDA EN HUERTAS ESCOLARES DEL DPTO. DR. MANUEL BELGRANO</t>
+  </si>
+  <si>
+    <t>MODELADO DE PRECIOS MINORISTAS DE HORTALIZAS EN JUJUY: UN ENFOQUE BASADO EN MECANISMOS DE TRANSMISIÓN DE PRECIOS CON VECM</t>
+  </si>
+  <si>
+    <t>PROMOCIÓN DE PRÁCTICAS SUSTENTABLES EN SISTEMAS HORTÍCOLAS: EXTRACTOS VEGETALES CON CAPACIDAD BIOENRAIZANTE, BIOFERTILIZANTE Y BIOPROTECTORA</t>
+  </si>
+  <si>
+    <t>HUERTA AGROECOLOGICA ESCOLAR: EL HUERTO DE COLORES</t>
+  </si>
+  <si>
+    <t>EDUCACIÓN ALIMENTARIA EN LA FORMACIÓN DEL LICENCIADO EN BROMATOLOGÍA: EXPERIENCIAS DE CAPACITACIÓN EN CONTEXTOS REALES</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Septiembre</t>
+  </si>
+  <si>
+    <t>ESTUDIOS PRELIMINARES SOBRE LA PRESENCIA DE BACTERIAS DEL GÉNERO Pseudomonas spp. EN RÍOS DE LA QUEBRADA DE HUMAHUACA, DURANTE ÉPOCA LLUVIOSA</t>
+  </si>
+  <si>
+    <t>DINÁMICA DE LA RESTAURACIÓN PASIVA, A PARTIR DE LA REGENERACIÓN, EN UN BOSQUE DISTURBADO DE LA SELVA PEDEMONTANA DE YUNGAS</t>
+  </si>
+  <si>
+    <t>EL PODCAST Y LA RADIO EN VIVO COMO HERRAMIENTAS PEDAGÓGICAS PARA GESTIÓN AMBIENTAL</t>
+  </si>
+  <si>
+    <t>ESTIMACIÓN DE ÍNDICES DE PRECIOS MAYORISTAS DE LAS PRINCIPALES FRUTAS Y HORTALIZAS RELEVADAS EN EL MERCADO FORMADOR DE PRECIOS DE LA REGIÓN DEL NOA ARGENTINO</t>
+  </si>
+  <si>
+    <t>TENDIENDO PUENTES ENTRE UNIVERSIDAD Y COMUNIDAD - PROYECTO “CRECE JUNTO A TU ÁRBOL”, VOLUNTARIADO UNIVERSITARIO</t>
+  </si>
+  <si>
+    <t>MANITAS LIMPIAS SALVAN VIDAS</t>
+  </si>
+  <si>
+    <t>FACTORES QUE INFLUYEN EN LAS DIFICULTADES DE APRENDIZAJE EN QUÍMICA GENERAL: PERCEPCIONES DE ESTUDIANTES DE BROMATOLOGÍA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Septiembre</t>
+  </si>
+  <si>
+    <t>IMPLEMENTACIÓN DEL APRENDIZAJE BASADO EN PROYECTOS EN LAS ASIGNATURAS BIOESTADÍSTICA (LICENCIATURA EN CIENCIAS BIOLÓGICAS) Y ESTADÍSTICA (LICENCIATURA EN DESARROLLO RURAL) DE LA UNJU</t>
+  </si>
+  <si>
+    <t>COMPOSICIÓN QUÍMICA DE ACEITES ESENCIALES DE ROMERO (Rosmarinus officinalis) Y TOMILLO (Thymus vulgaris). ESTUDIO DE SUS PROPIEDADES ANTIMICROBIANAS FRENTE A BACTERIAS GRAM NEGATIVAS</t>
+  </si>
+  <si>
+    <t>CARACTERIZACIÓN FISICOQUÍMICA DE PELÍCULAS COMESTIBLES A BASE DE ALMIDÓN DE PAPA Y ÁCIDO CÍTRICO COMO ADITIVO</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN DE PRÁCTICAS DEL USO DE SAL Y CONOCIMIENTOS EN PANADERÍAS DE LA PROVINCIA DE JUJUY</t>
+  </si>
+  <si>
+    <t>CONTROL DE CALIDAD EN FRUTOS DE POMELO (Citrus paradisi): EVALUACIÓN DE LA CAPACIDAD DEL PROCESO EN PRECOSECHA</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN IN VIVO DE EXTRACTOS DE PROPÓLEOS FRENTE A NOSEMA SP. EN APIS MELLIFERA DE LA PROVINCIA DE JUJUY</t>
   </si>
   <si>
     <r>
@@ -112,14 +117,14 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ICTIOFAUNA DEL RÍO XIBI-XIBI (JUJUY): UNA APROXIMACIÓN AL CONOCIMIENTO DE SU DIVERSIDAD Y DISTRIBUCIÓN</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>ICTIOFAUNA DEL RÍO XIBI-XIBI (JUJUY): UNA APROXIMACIÓN AL CONOCIMIENTO DE SU DIVERSIDAD Y DISTRIBUCIÓN</t>
     </r>
   </si>
   <si>
@@ -135,64 +140,64 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EVALUACIÓN DEL EFECTO CITOTOXICO DE MUÑA MUÑA (</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>EVALUACIÓN DEL EFECTO CITOTOXICO DE MUÑA MUÑA (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-BoldItalic"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CLINOPODIUM GILLIESII</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) SOBRE GORGOJOS DEL POROTO (</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
+      <t>CLINOPODIUM GILLIESII</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>) SOBRE GORGOJOS DEL POROTO (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-BoldItalic"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">ACANTHOSCELIDES OBTECTUS</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Martes 23 de Septiembre</t>
+      <t>ACANTHOSCELIDES OBTECTUS</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Martes 23 de Septiembre</t>
   </si>
   <si>
     <r>
@@ -207,14 +212,14 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">REGULACIÓN ALIMENTARIA Y PERCEPCIONES EN FERIAS POPULARES DE JUJUY</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>REGULACIÓN ALIMENTARIA Y PERCEPCIONES EN FERIAS POPULARES DE JUJUY</t>
     </r>
   </si>
   <si>
@@ -230,7 +235,7 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-Bold"/>
@@ -241,8 +246,8 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <i val="true"/>
+        <b/>
+        <i/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-BoldItalic"/>
@@ -253,14 +258,14 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(GUARÁN-GUARÁN) EN JUJUY</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(GUARÁN-GUARÁN) EN JUJUY</t>
     </r>
   </si>
   <si>
@@ -276,14 +281,14 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HERRAMIENTAS PARA LA GESTIÓN SUSTENTABLE DEL ARBOLADO URBANO - METÁN, SALTA</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>HERRAMIENTAS PARA LA GESTIÓN SUSTENTABLE DEL ARBOLADO URBANO - METÁN, SALTA</t>
     </r>
   </si>
   <si>
@@ -299,19 +304,19 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PRÁCTICAS AGROECOLÓGICAS DE CONTROL SANITARIO EN EL CULTIVO DE PAPA (</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>PRÁCTICAS AGROECOLÓGICAS DE CONTROL SANITARIO EN EL CULTIVO DE PAPA (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-BoldItalic"/>
@@ -322,7 +327,7 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-Bold"/>
@@ -333,26 +338,26 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <i val="true"/>
+        <b/>
+        <i/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-BoldItalic"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">SPUNTA</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) EN LA ESCUELA PROVINCIAL AGROTECNCIA N°1 EL BRETE-PALPALA</t>
+      <t>SPUNTA</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>) EN LA ESCUELA PROVINCIAL AGROTECNCIA N°1 EL BRETE-PALPALA</t>
     </r>
   </si>
   <si>
@@ -368,14 +373,14 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FACTORES QUE INCIDEN EN LA DESERCIÓN Y REPROBACIÓN DE LOS ESTUDIANTES EN LA MATERIA DE ÁLGEBRA Y GEOMETRÍA ANALÍTICA EN LA FACULTAD DE CIENCIAS AGRARIAS.</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>FACTORES QUE INCIDEN EN LA DESERCIÓN Y REPROBACIÓN DE LOS ESTUDIANTES EN LA MATERIA DE ÁLGEBRA Y GEOMETRÍA ANALÍTICA EN LA FACULTAD DE CIENCIAS AGRARIAS.</t>
     </r>
   </si>
   <si>
@@ -391,19 +396,19 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CARACTERIZACIÓN MORFOLÓGICA Y FÍSICA DE ACCESIONES CRIOLLAS DE HABAS (</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>CARACTERIZACIÓN MORFOLÓGICA Y FÍSICA DE ACCESIONES CRIOLLAS DE HABAS (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-BoldItalic"/>
@@ -414,14 +419,14 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">L.)</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>L.)</t>
     </r>
   </si>
   <si>
@@ -437,19 +442,19 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EVALUACIÓN DE DIFERENTES INDICADORES DE CALIDAD DE GRANO EN UN GENOTIPO DE SOJA (</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <i val="true"/>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>EVALUACIÓN DE DIFERENTES INDICADORES DE CALIDAD DE GRANO EN UN GENOTIPO DE SOJA (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-BoldItalic"/>
@@ -460,14 +465,14 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(L) CULTIVADO EN AMBIENTES CONTRASTANTES</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(L) CULTIVADO EN AMBIENTES CONTRASTANTES</t>
     </r>
   </si>
   <si>
@@ -483,7 +488,7 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-Bold"/>
@@ -494,8 +499,8 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <i val="true"/>
+        <b/>
+        <i/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri-BoldItalic"/>
@@ -506,14 +511,14 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri-Bold"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(ASPLENIACEAE) DE LAS YUNGAS ARGENTINAS, MEDIANTE LA APLICACION DE TECNICAS DE LABORATORIO CONVENCIONALES.</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri-Bold"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(ASPLENIACEAE) DE LAS YUNGAS ARGENTINAS, MEDIANTE LA APLICACION DE TECNICAS DE LABORATORIO CONVENCIONALES.</t>
     </r>
   </si>
   <si>
@@ -523,17 +528,17 @@
     <t xml:space="preserve">MAPA DE FERTILIDAD CON USO DE VARIABLES FÍSICAS-QUÍMICAS DEL SUELO DEL CAMPO EXPERIMENTAL DR. EMILIO NAVEA, FCA-UNJu </t>
   </si>
   <si>
-    <t xml:space="preserve">CONTROL DE CALIDAD FÍSICO-QUÍMICA EN VINOS ELABORADOS EN UNA BODEGA BOUTIQUE DE LA PROVINCIA DE JUJUY</t>
+    <t>CONTROL DE CALIDAD FÍSICO-QUÍMICA EN VINOS ELABORADOS EN UNA BODEGA BOUTIQUE DE LA PROVINCIA DE JUJUY</t>
+  </si>
+  <si>
+    <t>COMPARACIÓN DE ÍNDICES DE SEQUÍA BASADOS EN LA PRECIPITACIÓN PARA LA PROVINCIA DE JUJUY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,22 +547,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri-Bold"/>
@@ -565,8 +555,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <i val="true"/>
+      <b/>
+      <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri-BoldItalic"/>
@@ -574,7 +564,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -597,7 +587,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -605,65 +595,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -722,60 +669,76 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -807,7 +770,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -831,7 +794,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -891,411 +854,416 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C1048576"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="91.98"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" customWidth="1"/>
+    <col min="3" max="3" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" spans="1:3" s="1" customFormat="1">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:3" s="1" customFormat="1">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:3" s="1" customFormat="1">
+      <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" spans="1:3" s="1" customFormat="1">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:3" s="1" customFormat="1">
+      <c r="A6" s="1">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:3" s="1" customFormat="1">
+      <c r="A7" s="1">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:3" s="1" customFormat="1">
+      <c r="A8" s="1">
         <v>1</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:3" s="1" customFormat="1">
+      <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:3" s="1" customFormat="1">
+      <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:3" s="1" customFormat="1">
+      <c r="A11" s="1">
         <v>2</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:3" s="1" customFormat="1">
+      <c r="A12" s="1">
         <v>2</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
+    <row r="13" spans="1:3" s="1" customFormat="1">
+      <c r="A13" s="1">
         <v>2</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:3" s="1" customFormat="1">
+      <c r="A14" s="1">
         <v>2</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
+    <row r="15" spans="1:3" s="1" customFormat="1">
+      <c r="A15" s="1">
         <v>2</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:3" s="1" customFormat="1">
+      <c r="A16" s="1">
+        <v>3</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="1:3" s="1" customFormat="1">
+      <c r="A17" s="1">
+        <v>3</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="1:3" s="1" customFormat="1">
+      <c r="A18" s="1">
+        <v>3</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" s="3" t="s">
+    <row r="19" spans="1:3" s="1" customFormat="1">
+      <c r="A19" s="1">
+        <v>3</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A20" s="1">
+        <v>3</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A21" s="1">
+        <v>3</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="3" t="s">
+    <row r="22" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A22" s="1">
+        <v>3</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A23" s="1">
+        <v>3</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="n">
+    <row r="24" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A24" s="1">
         <v>4</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="n">
+    <row r="25" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A25" s="1">
         <v>4</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A26" s="1">
         <v>4</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="n">
+    <row r="27" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A27" s="1">
         <v>4</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A28" s="1">
         <v>4</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="n">
+    <row r="29" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A29" s="1">
         <v>4</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="n">
+    <row r="30" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A30" s="1">
         <v>4</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="n">
+    <row r="31" spans="1:3" s="1" customFormat="1" ht="15" customHeight="1">
+      <c r="A31" s="1">
         <v>4</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="n">
+    <row r="32" spans="1:3" ht="30">
+      <c r="A32" s="1">
         <v>2</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="n">
+    <row r="33" spans="1:3" ht="30">
+      <c r="A33" s="1">
         <v>1</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="5" t="s">
+      <c r="B33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="n">
+    <row r="34" spans="1:3" ht="15" customHeight="1">
+      <c r="A34" s="1">
         <v>4</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" spans="1:3" ht="15" customHeight="1">
+      <c r="A35" s="1">
+        <v>4</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="1048574" ht="12.75" customHeight="1"/>
+    <row r="1048575" ht="12.75" customHeight="1"/>
+    <row r="1048576" ht="12.75" customHeight="1"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>